--- a/artfynd/A 53600-2025 artfynd.xlsx
+++ b/artfynd/A 53600-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133233068</v>
       </c>
       <c r="B2" t="n">
-        <v>56766</v>
+        <v>56773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133233062</v>
       </c>
       <c r="B3" t="n">
-        <v>60497</v>
+        <v>60504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53600-2025 artfynd.xlsx
+++ b/artfynd/A 53600-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133233068</v>
       </c>
       <c r="B2" t="n">
-        <v>56773</v>
+        <v>56783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>133233062</v>
       </c>
       <c r="B3" t="n">
-        <v>60504</v>
+        <v>60514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53600-2025 artfynd.xlsx
+++ b/artfynd/A 53600-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,7 +682,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -780,7 +780,7 @@
         <v>133233062</v>
       </c>
       <c r="B3" t="n">
-        <v>60514</v>
+        <v>60521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,6 +876,346 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125403388</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58393</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Joakim, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>500533</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6596644</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125403387</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Joakim, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500533</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6596644</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Lif</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133233082</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Älvestorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500804</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6596805</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Magnus Sjölund</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53600-2025 artfynd.xlsx
+++ b/artfynd/A 53600-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133233068</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133233062</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125403388</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125403387</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,8 +1241,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133233082</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>